--- a/data-manipulation-scripts/sheets-cleanup/sheets/BALANCIM VALVULAS.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BALANCIM VALVULAS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>BALANCIM VALVULAS LAQUILA (PAR) CG125 1992 A 1998/ TITAN KS</t>
-  </si>
-  <si>
-    <t>7908073700465</t>
-  </si>
-  <si>
-    <t>EIXO BALANCIM SMARTFOX CG125 TODAY 1995 A 2004/ TITAN KS/ FAN 2005 A 2008</t>
   </si>
   <si>
     <t>7899468026881</t>
@@ -450,7 +444,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="3">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -462,9 +456,11 @@
         <v>17</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="3">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
@@ -476,9 +472,7 @@
       <c r="C9" s="3">
         <v>2.0</v>
       </c>
-      <c r="D9" s="3">
-        <v>120.0</v>
-      </c>
+      <c r="D9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -492,37 +486,31 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
+    <row r="19">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="20" ht="72.0" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A28" s="5"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
     </row>
@@ -532,23 +520,23 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
     </row>
-    <row r="30">
-      <c r="A30" s="5"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+    <row r="30" ht="18.75" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="5"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" ht="18.75" customHeight="1">
+    <row r="32">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="D32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="2"/>
@@ -569,52 +557,52 @@
       <c r="D35" s="4"/>
     </row>
     <row r="36">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
     </row>
     <row r="39">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="4"/>
     </row>
     <row r="40">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="4"/>
     </row>
     <row r="43">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
     </row>
     <row r="44">
       <c r="A44" s="5"/>
@@ -629,22 +617,22 @@
       <c r="D45" s="4"/>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="4"/>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="3"/>
     </row>
     <row r="49">
       <c r="A49" s="2"/>
@@ -653,16 +641,16 @@
       <c r="D49" s="3"/>
     </row>
     <row r="50">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="A50" s="5"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
     </row>
     <row r="51">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="A51" s="5"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
     </row>
     <row r="52">
       <c r="A52" s="5"/>
@@ -6322,18 +6310,6 @@
       <c r="C994" s="4"/>
       <c r="D994" s="4"/>
     </row>
-    <row r="995">
-      <c r="A995" s="5"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="5"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/BALANCIM VALVULAS.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BALANCIM VALVULAS.xlsx
@@ -398,7 +398,9 @@
       <c r="C3" s="3">
         <v>5.0</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
@@ -410,7 +412,9 @@
       <c r="C4" s="3">
         <v>1.0</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
@@ -422,7 +426,9 @@
       <c r="C5" s="3">
         <v>1.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3">
+        <v>188.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
@@ -434,7 +440,9 @@
       <c r="C6" s="3">
         <v>2.0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="3">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
@@ -446,7 +454,9 @@
       <c r="C7" s="3">
         <v>5.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="3">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
@@ -472,7 +482,9 @@
       <c r="C9" s="3">
         <v>2.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="3">
+        <v>125.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -484,7 +496,9 @@
       <c r="C10" s="3">
         <v>2.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="3">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2"/>
